--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/02. Trả bảo hành/TBH_AnhTuanNB(NamĐịnh)_200826.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/02. Trả bảo hành/TBH_AnhTuanNB(NamĐịnh)_200826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 08\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB20ACA6-B3AE-43F1-973C-CD2754CD0DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F552FF-1B22-4FC0-A60E-B0B4A6EB5358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -463,6 +463,60 @@
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -483,60 +537,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -971,25 +971,25 @@
       <c r="I4" s="51"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
       <c r="E6" s="8"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -999,12 +999,12 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
       <c r="E7" s="8"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -1012,12 +1012,12 @@
       <c r="I7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
       <c r="E8" s="8"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
@@ -1025,12 +1025,12 @@
       <c r="I8" s="9"/>
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
@@ -1068,53 +1068,53 @@
       <c r="J10" s="6"/>
     </row>
     <row r="11" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="56">
+      <c r="A11" s="38">
         <v>1</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57" t="s">
+      <c r="D11" s="39"/>
+      <c r="E11" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="57" t="s">
+      <c r="F11" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="57" t="s">
+      <c r="G11" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="57" t="s">
+      <c r="H11" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="58"/>
+      <c r="I11" s="40"/>
       <c r="J11" s="6"/>
     </row>
     <row r="12" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="52">
+      <c r="A12" s="34">
         <v>2</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54" t="s">
+      <c r="D12" s="36"/>
+      <c r="E12" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54" t="s">
+      <c r="F12" s="36"/>
+      <c r="G12" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="54" t="s">
+      <c r="H12" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="55"/>
+      <c r="I12" s="37"/>
       <c r="J12" s="6"/>
     </row>
     <row r="13" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1129,34 +1129,34 @@
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="39" t="s">
+      <c r="G14" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
     </row>
     <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
       <c r="E15" s="31"/>
       <c r="F15" s="32"/>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
     </row>
     <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="21"/>
@@ -1203,19 +1203,19 @@
       <c r="I19" s="28"/>
     </row>
     <row r="20" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
       <c r="E20" s="18"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
     </row>
     <row r="21" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
@@ -1229,17 +1229,12 @@
       <c r="I21" s="30"/>
     </row>
     <row r="23" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
     </row>
     <row r="62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="A6:D6"/>
@@ -1252,6 +1247,11 @@
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
